--- a/asignaturas/fisica/propuesta/Propuesta_Fisica_G02-G04.xlsx
+++ b/asignaturas/fisica/propuesta/Propuesta_Fisica_G02-G04.xlsx
@@ -547,11 +547,11 @@
       </c>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>7. Calor, luz y electricidad.</t>
+          <t>7. Calor y sonido.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>CO 2, SG 4 (Calentamiento y enfriamiento); SG 4, UY 3 (Temperatura y escalas termométricas); SG 4, UY 5 (Equilibrio térmico y ley cero); T4_27-P2.2 Calentamiento y enfriamiento (reforzar: 1 tema, débil); prerrequisito: Calentamiento y enfriamiento (G02-2.6, acción 12)</t>
+          <t>AU 2, CO 2, ENG 6, SG 4 (Calentamiento y enfriamiento; destino 3.°); ENG 2, SG 4, UY 3 (Temperatura y escalas termométricas; destino 3.°); AU 2, ENG 6, SG 4, UY 5 (Equilibrio térmico y ley cero, nivel intuitivo); T4_27-P2.2 Calentamiento y enfriamiento (reforzar: 1 tema, débil); prerrequisito: Calentamiento y enfriamiento (G02-2.6, acción 12)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Hoy el termómetro llega en 6.° y el equilibrio térmico en 9.°; Singapur y Uruguay los enseñan entre 3.° y 5.°. Se trabaja solo en grados Celsius: las escalas quedan en 6.°. Se paga con la fusión 8.</t>
+          <t>Inglaterra, Australia y Colombia lo trabajan en 2.°; El Salvador, en 6.° (termómetro) y 9.° (equilibrio). Va en 3.°, el destino de los candidatos, solo en grados Celsius. Se paga con la fusión 8.</t>
         </is>
       </c>
     </row>
@@ -619,12 +619,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>CO 2, SG 3, UY 5 (Imanes y polos magnéticos); T4_27-P4.2 Atracción y repulsión magnética (reforzar: 1 tema, débil); prerrequisito: Fuerzas de contacto y a distancia (G03-1.3 a 1.5, mismo grado)</t>
+          <t>AU 3, CO 2, ENG 2, SG 3, UY 5 (Imanes y polos magnéticos); ENG 2, SG 3 (Materiales magnéticos); T4_27-P4.2 Atracción y repulsión magnética (reforzar: 1 tema, débil); prerrequisito: Fuerzas de contacto y a distancia (G03-1.3 a 1.5, mismo grado)</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Hoy los polos magnéticos llegan en 6.°, después del campo magnético de 5.°. Colombia y Singapur los enseñan en 2.° y 3.°. Va después de las fuerzas a distancia. Se paga con la fusión 6.</t>
+          <t>Los cinco países enseñan los imanes entre 2.° y 5.° (Inglaterra y Colombia en 2.°); El Salvador, en 6.°. Va después de las fuerzas a distancia, con los materiales magnéticos. Se paga con la fusión 6.</t>
         </is>
       </c>
     </row>
@@ -653,12 +653,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7. El sonido. (3.°); la parte de vibraciones queda en 2. Energía. (2.°)</t>
+          <t>7. Calor y sonido. (3.°); la parte de vibraciones queda en 2. Energía. (2.°)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2.5. Exploración de sonidos producidos al hacer vibrar objetos del entorno (ligas, vasos con agua, tambores caseros). (se mantiene en 2.°) | 7.1. Comparación de sonidos por su tono y su intensidad y exploración del eco.</t>
+          <t>2.5. Exploración de sonidos producidos al hacer vibrar objetos del entorno (ligas, vasos con agua, tambores caseros). (se mantiene en 2.°) | 7.2. Comparación de sonidos por su tono y su intensidad y exploración del eco.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -697,36 +697,36 @@
       </c>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>7. Calor, luz y electricidad.</t>
+          <t>1. Medidas y fuerzas. (después de 1.6)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>7.2. Experimentación con la reflexión de la luz en espejos y superficies brillantes.</t>
+          <t>1.8. Experimentación con la fricción y la resistencia del aire que frenan el movimiento.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Dirige un haz de luz con un espejo hacia un blanco y explica con un dibujo de rayos por qué vemos reflejos en el agua, los espejos y los metales pulidos.</t>
+          <t>Compara la distancia que recorre un carrito sobre superficies distintas y cómo cae una hoja extendida y una arrugada, y explica qué fuerza se opone al movimiento en cada caso.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Reflexión de la luz</t>
+          <t>Fricción y resistencia del aire</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>CO 3, SG 4, UY 4 (Reflexión de la luz); sin bloqueos</t>
+          <t>AU 3, ENG 2, SG 6 (Fricción y resistencia del aire; destino 3.°); prerrequisito: Fuerzas de contacto y a distancia (G03-1.3 a 1.5, mismo grado)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Los tres países enseñan la reflexión en 3.° o 4.°; El Salvador, en 10.°. No tiene bloqueos y continúa lo trabajado en 2.° sobre fuentes de luz, sombras y materiales. Se paga con la fusión 7.</t>
+          <t>Inglaterra y Australia la enseñan en 2.° y 3.°; El Salvador, en 10.°. Completa la unidad de fuerzas de 3.° con la fuerza que se opone al movimiento. Se paga con la fusión 7.</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7. Calor, luz y electricidad.</t>
+          <t>7. La luz.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7.3. Clasificación de materiales en conductores y aislantes eléctricos con un probador de circuito sencillo.</t>
+          <t>7.1. Experimentación con la reflexión de la luz en espejos y superficies brillantes.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Comprueba con un probador (pila, foco y cables) qué materiales dejan pasar la corriente y relaciona el resultado con el uso de metal en los cables y de plástico en su recubrimiento.</t>
+          <t>Dirige un haz de luz con un espejo hacia un blanco y explica con un dibujo de rayos por qué vemos reflejos en el agua, los espejos y los metales pulidos.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Conductores y aislantes eléctricos</t>
+          <t>Reflexión de la luz</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>CO 4, SG 5 (Conductores y aislantes eléctricos); sin bloqueos</t>
+          <t>AU 4, CO 3, ENG 2, SG 4, UY 4 (Reflexión de la luz); sin bloqueos</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Hoy solo aparece en 11.° (G11-FIS-U6-6.3), después del circuito simple de 6.°. Colombia lo enseña en 4.°. El probador lo arma el docente. Se paga con la fusión 7 (segundo tema liberado).</t>
+          <t>Los cinco países enseñan la reflexión entre 2.° y 4.°; El Salvador, en 10.°. No tiene bloqueos y continúa lo trabajado en 2.° sobre fuentes de luz y sombras. Se paga con la fusión 7.</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>prerrequisito: Gravedad: atracción hacia la Tierra (de Masa y peso; hoy en ningún grado); CO 4, UY 5 (Ley de gravitación universal, en versión cualitativa)</t>
+          <t>corregir_secuencia: Masa y peso (2.°) necesita Gravedad: atracción hacia la Tierra (hoy en ningún grado)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>La gravedad no aparece en ningún grado de la malla. Se nombra en las fuerzas a distancia de forma cualitativa; la ley de gravitación sigue en 10.°. Los imanes pasan al tema nuevo 1.7.</t>
+          <t>La gravedad no aparece en ningún grado de la malla. Se nombra de forma cualitativa en las fuerzas a distancia de 3.°; la ley de gravitación sigue en 10.°. Los imanes pasan al tema nuevo 1.7.</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>CO 2, UY 3 (Sistema Internacional de Unidades); prerrequisito: Medición de magnitudes con instrumentos (2.°)</t>
+          <t>CO 2, ENG 6, UY 3 (Sistema Internacional de Unidades; destino 3.°); prerrequisito: Medición de magnitudes con instrumentos (2.°)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1377,10 +1377,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>19</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>18</v>
       </c>
       <c r="D2" s="4">
         <f>C2-B2</f>
@@ -1403,7 +1403,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="4">
         <f>C3-B3</f>
@@ -1426,7 +1426,7 @@
         <v>9</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4" s="4">
         <f>C4-B4</f>

--- a/asignaturas/fisica/propuesta/Propuesta_Fisica_G02-G04.xlsx
+++ b/asignaturas/fisica/propuesta/Propuesta_Fisica_G02-G04.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -556,27 +556,27 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>7.1. Medición de la temperatura de objetos que se calientan o se enfrían al estar en contacto.</t>
+          <t>7.1. Medición con termómetro de la temperatura de objetos que se calientan o se enfrían.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Registra con un termómetro, cada pocos minutos, la temperatura de un vaso de agua tibia colocado en agua fría y explica que el objeto caliente se enfría y el frío se calienta hasta igualarse.</t>
+          <t>Registra con un termómetro, cada pocos minutos, la temperatura de un vaso de agua tibia colocado en agua fría, expresa cada lectura en grados Celsius y describe cómo cambia.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Calentamiento y enfriamiento, Temperatura y escalas termométricas, Equilibrio térmico y ley cero</t>
+          <t>Temperatura y escalas termométricas, Calentamiento y enfriamiento</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>AU 2, CO 2, ENG 6, SG 4 (Calentamiento y enfriamiento; destino 3.°); ENG 2, SG 4, UY 3 (Temperatura y escalas termométricas; destino 3.°); AU 2, ENG 6, SG 4, UY 5 (Equilibrio térmico y ley cero, nivel intuitivo); T4_27-P2.2 Calentamiento y enfriamiento (reforzar: 1 tema, débil); prerrequisito: Calentamiento y enfriamiento (G02-2.6, acción 12)</t>
+          <t>ENG 2, SG 4, UY 3 (Temperatura y escalas termométricas; destino 3.°, sin bloqueos); T4_27-P2.2 Calentamiento y enfriamiento (reforzar: 1 tema, débil); prerrequisito: Calentamiento y enfriamiento (G02-2.6, acción 17); prerrequisito: Medición de magnitudes con instrumentos (2.° y 3.°)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Inglaterra, Australia y Colombia lo trabajan en 2.°; El Salvador, en 6.° (termómetro) y 9.° (equilibrio). Va en 3.°, el destino de los candidatos, solo en grados Celsius. Se paga con la fusión 8.</t>
+          <t>Inglaterra la enseña en 2.° y Singapur en 4.°; El Salvador, en 6.°. Va en 3.°, el destino de los candidatos, solo en grados Celsius. El equilibrio térmico queda en 9.°. Se paga con la fusión 9.</t>
         </is>
       </c>
     </row>
@@ -619,12 +619,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>AU 3, CO 2, ENG 2, SG 3, UY 5 (Imanes y polos magnéticos); ENG 2, SG 3 (Materiales magnéticos); T4_27-P4.2 Atracción y repulsión magnética (reforzar: 1 tema, débil); prerrequisito: Fuerzas de contacto y a distancia (G03-1.3 a 1.5, mismo grado)</t>
+          <t>AU 3, CO 2, ENG 2, JP 2, SG 3, UY 5 (Imanes y polos magnéticos; destino 3.°); ENG 2, JP 2, SG 3 (Materiales magnéticos; destino 2.°, se ubica en 3.° por su bloqueo Imanes y polos magnéticos); T4_27-P4.2 Atracción y repulsión magnética (reforzar: 1 tema, débil); prerrequisito: Fuerzas de contacto y a distancia (G03-1.3 a 1.5, mismo grado)</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Los cinco países enseñan los imanes entre 2.° y 5.° (Inglaterra y Colombia en 2.°); El Salvador, en 6.°. Va después de las fuerzas a distancia, con los materiales magnéticos. Se paga con la fusión 6.</t>
+          <t>Seis países, cuatro de alto desempeño, enseñan los imanes entre 2.° y 5.°; El Salvador, en 6.°. Los materiales magnéticos no pueden ir en 2.°: necesitan los polos y las fuerzas a distancia de 3.°. Se paga con la fusión 7.</t>
         </is>
       </c>
     </row>
@@ -634,51 +634,45 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>dividir</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>G02-CIE-U2-2.5</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7. Calor y sonido. (3.°); la parte de vibraciones queda en 2. Energía. (2.°)</t>
+          <t>1. Medidas y fuerzas. (después de 1.6)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2.5. Exploración de sonidos producidos al hacer vibrar objetos del entorno (ligas, vasos con agua, tambores caseros). (se mantiene en 2.°) | 7.2. Comparación de sonidos por su tono y su intensidad y exploración del eco.</t>
+          <t>1.8. Experimentación con la fricción y la resistencia del aire que frenan el movimiento.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Muestra, tocando ligas, tambores y vasos con agua, que todo sonido se produce porque algo vibra. | Ordena sonidos de instrumentos caseros de grave a agudo y de débil a fuerte, y explica el eco como un sonido que rebota en una superficie lejana.</t>
+          <t>Compara la distancia que recorre un carrito sobre superficies distintas y cómo cae una hoja extendida y una arrugada, y explica qué fuerza se opone al movimiento en cada caso.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>El sonido se produce por vibraciones, Características del sonido: tono, intensidad y eco</t>
+          <t>Fricción y resistencia del aire</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>T4_27-P3.2 El sonido en la vida diaria (reforzar: 1 tema, débil); G02-2.5 ya trabaja los dos conceptos en un solo tema</t>
+          <t>AU 3, ENG 2, SG 6 (Fricción y resistencia del aire; destino 3.°); prerrequisito: Fuerzas de contacto y a distancia (G03-1.3 a 1.5, mismo grado)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Es el único tema de sonido del ciclo y reúne dos conceptos. La vibración queda en 2.°; tono, intensidad y eco pasan a 3.°. El archivo no trae países para este concepto (decisión abierta). Se paga con la fusión 9.</t>
+          <t>Inglaterra y Australia la enseñan en 2.° y 3.°; El Salvador, en 10.°. Completa la unidad de fuerzas de 3.° con la fuerza que se opone al movimiento. Se paga con la fusión 8.</t>
         </is>
       </c>
     </row>
@@ -697,36 +691,36 @@
       </c>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1. Medidas y fuerzas. (después de 1.6)</t>
+          <t>7. La luz.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>1.8. Experimentación con la fricción y la resistencia del aire que frenan el movimiento.</t>
+          <t>7.1. Experimentación con la reflexión de la luz en espejos y superficies brillantes.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Compara la distancia que recorre un carrito sobre superficies distintas y cómo cae una hoja extendida y una arrugada, y explica qué fuerza se opone al movimiento en cada caso.</t>
+          <t>Dirige un haz de luz con un espejo hacia un blanco y explica con un dibujo de rayos por qué vemos reflejos en el agua, los espejos y los metales pulidos.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Fricción y resistencia del aire</t>
+          <t>Reflexión de la luz</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>AU 3, ENG 2, SG 6 (Fricción y resistencia del aire; destino 3.°); prerrequisito: Fuerzas de contacto y a distancia (G03-1.3 a 1.5, mismo grado)</t>
+          <t>AU 4, CO 3, ENG 2, JP 2, SG 4, UY 4 (Reflexión de la luz; destino 4.°); prerrequisito: Fuentes de luz, propagación y sombras (G02-2.9)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Inglaterra y Australia la enseñan en 2.° y 3.°; El Salvador, en 10.°. Completa la unidad de fuerzas de 3.° con la fuerza que se opone al movimiento. Se paga con la fusión 7.</t>
+          <t>Seis países, cuatro de alto desempeño, la enseñan entre 2.° y 4.°; El Salvador, en 10.°. No tiene bloqueos y continúa las fuentes de luz de 2.°. Se paga con la fusión 8.</t>
         </is>
       </c>
     </row>
@@ -749,32 +743,32 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7. La luz.</t>
+          <t>1. Máquinas y energía. (después de 1.8)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7.1. Experimentación con la reflexión de la luz en espejos y superficies brillantes.</t>
+          <t>1.9. Clasificación de materiales en conductores y aislantes y construcción de circuitos eléctricos simples.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Dirige un haz de luz con un espejo hacia un blanco y explica con un dibujo de rayos por qué vemos reflejos en el agua, los espejos y los metales pulidos.</t>
+          <t>Prueba objetos del aula para clasificarlos en conductores y aislantes, arma un circuito con pila, cables y bombilla y explica por qué la bombilla solo enciende si el circuito está cerrado.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Reflexión de la luz</t>
+          <t>Conductores y aislantes eléctricos, Circuito eléctrico simple</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>AU 4, CO 3, ENG 2, SG 4, UY 4 (Reflexión de la luz); sin bloqueos</t>
+          <t>AU 5, CO 2, ENG 2, JP 2, SG 5, UY 5 (Circuito eléctrico simple; destino 4.°); bloqueo: Conductores y aislantes eléctricos (hoy 11.°): se crea en el mismo tema, antes del circuito; prerrequisito para Corriente, voltaje y resistencia (ENG 4, JP 3), que sigue en 6.°</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Los cinco países enseñan la reflexión entre 2.° y 4.°; El Salvador, en 10.°. No tiene bloqueos y continúa lo trabajado en 2.° sobre fuentes de luz y sombras. Se paga con la fusión 7.</t>
+          <t>Inglaterra y Japón arman circuitos en 2.°, Australia y Singapur en 5.°; El Salvador, en 6.°. Su bloqueo, los conductores, se trabaja primero en el mismo tema. Se paga con la fusión 10.</t>
         </is>
       </c>
     </row>
@@ -784,51 +778,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>fusionar</t>
+          <t>dividir</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>G04-CIE-U1-1.1, G04-CIE-U1-1.2</t>
+          <t>G02-CIE-U2-2.5</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1. Máquinas y energía.</t>
+          <t>7. Calor y sonido. (3.°); la parte de vibraciones queda en 2. Energía. (2.°)</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>1.1. Indagación y clasificación de las máquinas simples a partir de dispositivos del entorno.</t>
+          <t>2.5. Exploración de sonidos producidos al hacer vibrar objetos del entorno (ligas, vasos con agua, tambores caseros). (se mantiene en 2.°) | 7.2. Comparación de sonidos por su tono y su intensidad y exploración del eco.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Clasifica dispositivos del entorno (tijeras, rampa, polea, abrelatas) según el tipo de máquina simple y explica si facilitan el trabajo porque requieren menos fuerza o cambian su dirección.</t>
+          <t>Muestra, tocando ligas, tambores y vasos con agua, que todo sonido se produce porque algo vibra. | Ordena sonidos de instrumentos caseros de grave a agudo y de débil a fuerte, y explica el eco como un sonido que rebota en una superficie lejana.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Máquinas simples</t>
+          <t>El sonido se produce por vibraciones, Características del sonido: tono, intensidad y eco</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Máquinas simples: 6 temas en 4.° (G04-1.1 a 1.6)</t>
+          <t>T4_27-P3.2 El sonido en la vida diaria (reforzar: 1 tema, débil); G02-2.5 trabaja los dos conceptos en un solo tema</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Ambos temas definen y clasifican las máquinas simples. Unidos, liberan el tema que usa la acción 2.</t>
+          <t>Es el único tema de sonido del ciclo y reúne dos conceptos. La vibración queda en 2.°; tono, intensidad y eco pasan a 3.°. El archivo no trae países para este concepto (decisión abierta). Se paga con la fusión 11.</t>
         </is>
       </c>
     </row>
@@ -843,11 +837,11 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>G04-CIE-U1-1.4, G04-CIE-U1-1.5, G04-CIE-U1-1.6</t>
+          <t>G04-CIE-U1-1.1, G04-CIE-U1-1.2</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>4</v>
@@ -862,12 +856,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1.4. Construcción de una máquina compleja e identificación de las máquinas simples que la forman.</t>
+          <t>1.1. Indagación y clasificación de las máquinas simples a partir de dispositivos del entorno.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Construye con materiales reciclados una máquina compleja sencilla y señala las máquinas simples que la componen y la función de cada una.</t>
+          <t>Clasifica dispositivos del entorno (tijeras, rampa, polea, abrelatas) según el tipo de máquina simple y explica si facilitan el trabajo porque requieren menos fuerza o cambian su dirección.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -882,7 +876,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Los tres temas tratan la máquina compleja: concepto, análisis y construcción. Se integran en un proyecto. Liberan los dos temas que usan las acciones 4 y 5.</t>
+          <t>Ambos temas definen y clasifican las máquinas simples. Unidos, liberan el tema que usa la acción 2.</t>
         </is>
       </c>
     </row>
@@ -897,11 +891,11 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>G04-CIE-U1-1.8, G04-CIE-U1-1.9</t>
+          <t>G04-CIE-U1-1.4, G04-CIE-U1-1.5, G04-CIE-U1-1.6</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>4</v>
@@ -916,27 +910,27 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>1.8. Identificación de las fuentes y formas de energía de los objetos tecnológicos y su relación con la utilidad del dispositivo.</t>
+          <t>1.4. Construcción de una máquina compleja e identificación de las máquinas simples que la forman.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Elabora un cuadro con objetos de uso diario, su fuente de energía y la forma en que la transforman (luz, calor, movimiento o sonido).</t>
+          <t>Construye con materiales reciclados una máquina compleja sencilla y señala las máquinas simples que la componen y la función de cada una.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>La energía y sus usos, Formas de energía</t>
+          <t>Máquinas simples</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>La energía y sus usos: también en G02-2.1, 2.2 y 2.4</t>
+          <t>Máquinas simples: 6 temas en 4.° (G04-1.1 a 1.6)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Ambos temas trabajan los mismos dos conceptos sobre los mismos objetos. Unidos, liberan el tema que usa la acción 1.</t>
+          <t>Los tres temas tratan la máquina compleja: concepto, análisis y construcción. Se integran en un proyecto. Liberan los dos temas que usan las acciones 3 y 4.</t>
         </is>
       </c>
     </row>
@@ -951,46 +945,46 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>G02-CIE-U1-1.1, G02-CIE-U1-1.2</t>
+          <t>G04-CIE-U1-1.8, G04-CIE-U1-1.9</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. Materia.</t>
+          <t>1. Máquinas y energía.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1.1. Manipulación de instrumentos de medición para comparar magnitudes de objetos del entorno.</t>
+          <t>1.8. Identificación de las fuentes y formas de energía de los objetos tecnológicos y su relación con la utilidad del dispositivo.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Usa regla, balanza y recipiente graduado para medir objetos del entorno y distingue lo que se puede medir (largo, masa) de lo que solo se describe (color, textura).</t>
+          <t>Elabora un cuadro con objetos de uso diario, su fuente de energía y la forma en que la transforman (luz, calor, movimiento o sonido).</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Medición de magnitudes con instrumentos</t>
+          <t>La energía y sus usos, Formas de energía</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Medición de magnitudes con instrumentos: también en G02-5.2, G03-1.1 y G03-1.2</t>
+          <t>La energía y sus usos: también en G02-2.1, 2.2 y 2.4</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Ambos temas introducen la medición con el mismo concepto; uno con instrumentos y otro con la idea de magnitud. Unidos, liberan el tema que usa la acción 3.</t>
+          <t>Ambos temas trabajan los mismos dos conceptos sobre los mismos objetos. Unidos, liberan el tema que usa la acción 1.</t>
         </is>
       </c>
     </row>
@@ -1000,51 +994,51 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>fusionar</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>G03-CIE-U1-1.4</t>
+          <t>G02-CIE-U1-1.1, G02-CIE-U1-1.2</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1. Medidas y fuerzas.</t>
+          <t>1. Materia.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>1.4. Experimentación con fuerzas a distancia: la gravedad atrae los objetos hacia la Tierra.</t>
+          <t>1.1. Manipulación de instrumentos de medición para comparar magnitudes de objetos del entorno.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Explica, a partir de soltar objetos distintos, que todos caen porque la Tierra los atrae, y da otro ejemplo de fuerza que actúa sin contacto.</t>
+          <t>Usa regla, balanza y recipiente graduado para medir objetos del entorno y distingue lo que se puede medir (largo, masa) de lo que solo se describe (color, textura).</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Fuerzas de contacto y a distancia, Gravedad: atracción hacia la Tierra</t>
+          <t>Medición de magnitudes con instrumentos</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Masa y peso (2.°) necesita Gravedad: atracción hacia la Tierra (hoy en ningún grado)</t>
+          <t>Medición de magnitudes con instrumentos: también en G02-5.2, G03-1.1 y G03-1.2</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>La gravedad no aparece en ningún grado de la malla. Se nombra de forma cualitativa en las fuerzas a distancia de 3.°; la ley de gravitación sigue en 10.°. Los imanes pasan al tema nuevo 1.7.</t>
+          <t>Ambos temas introducen la medición con el mismo concepto; uno con instrumentos y otro con la idea de magnitud. Unidos, liberan el tema que usa la acción 5.</t>
         </is>
       </c>
     </row>
@@ -1054,16 +1048,16 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>fusionar</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>G02-CIE-U5-5.2</t>
+          <t>G02-CIE-U2-2.1-f3, G02-CIE-U2-2.2</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>2</v>
@@ -1073,32 +1067,32 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5. Objetos técnicos.</t>
+          <t>2. Energía.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5.2. Registro de la masa de objetos empleando una balanza.</t>
+          <t>2.1. Observación de fenómenos y dispositivos del entorno que usan energía e identificación de su fuente.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Compara y ordena objetos según su masa con la balanza construida en clase y registra los resultados en una tabla.</t>
+          <t>Describe fenómenos donde la energía se hace visible (viento, fuego, sol) y relaciona aparatos de la casa con la fuente de energía que los hace funcionar.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Medición de magnitudes con instrumentos</t>
+          <t>La energía y sus usos, Formas de energía</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Masa y peso (2.°) necesita Gravedad: atracción hacia la Tierra (nunca)</t>
+          <t>La energía y sus usos y Formas de energía: ambos temas trabajan los dos conceptos (también G02-2.4 y G04-1.8)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>En 2.° se trabaja solo la masa. La distinción entre masa y peso se deja para después de la gravedad (acción 10), en 4.° o 5.°.</t>
+          <t>Ambos temas introducen la energía con los mismos dos conceptos, uno con fenómenos y otro con aparatos. Unidos, liberan el tema que usa la acción 6 (sonido).</t>
         </is>
       </c>
     </row>
@@ -1113,46 +1107,46 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>G02-CIE-U2-2.6</t>
+          <t>G03-CIE-U1-1.4</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2. Energía.</t>
+          <t>1. Medidas y fuerzas.</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>2.6. Comparación de objetos colocados al sol y a la sombra para observar cómo se calientan y se enfrían.</t>
+          <t>1.4. Experimentación con fuerzas a distancia: la gravedad atrae los objetos hacia la Tierra.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Predice y comprueba al tacto qué objetos se calientan más al sol y cómo se enfrían al pasar a la sombra, y registra sus observaciones con dibujos.</t>
+          <t>Explica, a partir de soltar objetos distintos, que todos caen porque la Tierra los atrae, y da otro ejemplo de fuerza que actúa sin contacto.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Calentamiento y enfriamiento</t>
+          <t>Fuerzas de contacto y a distancia, Gravedad: atracción hacia la Tierra</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Conducción, convección y radiación (2.°) y Cambios de estado (2.°) necesitan Calentamiento y enfriamiento; T4_27-P2.2 Calentamiento y enfriamiento (reforzar: 1 tema, débil)</t>
+          <t>corregir_secuencia: Masa y peso (2.°) necesita Gravedad: atracción hacia la Tierra (hoy en ningún grado)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Se centra en calentar y enfriar y se retira la etiqueta de conducción, convección y radiación, impropia en 2.°. Queda como primer contacto con el concepto, antes de G02-1.8 y de la acción 1.</t>
+          <t>La gravedad no aparece en ningún grado de la malla. Se nombra de forma cualitativa en las fuerzas a distancia de 3.°; la ley de gravitación sigue en 10.°. Los imanes pasan al tema nuevo 1.7.</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1161,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>G02-CIE-U5-5.4</t>
+          <t>G02-CIE-U5-5.2</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1186,27 +1180,27 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5.4. Comprobación de la carga que soporta una estructura según su forma y sus materiales.</t>
+          <t>5.2. Registro de la masa de objetos empleando una balanza.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Agrega pesos a un modelo de puente o torre hasta que se deforma o cae y compara los resultados de dos diseños.</t>
+          <t>Compara y ordena objetos según su masa con la balanza construida en clase y registra los resultados en una tabla.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Fuerza como empuje o tirón</t>
+          <t>Medición de magnitudes con instrumentos</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Esfuerzo, deformación y módulo de Young (2.°) necesita Fuerza elástica y ley de Hooke (5.°)</t>
+          <t>corregir_secuencia: Masa y peso (2.°) necesita Gravedad: atracción hacia la Tierra (nunca)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>El tema no trabaja el módulo de Young: la etiqueta crea una secuencia invertida falsa. Se reformula como comparación de diseños, sin cuantificar el esfuerzo.</t>
+          <t>En 2.° se trabaja solo la masa. La distinción entre masa y peso se deja para después de la gravedad (acción 12), en 4.° o 5.°.</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1215,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>G02-CIE-U3-3.2</t>
+          <t>G02-CIE-U5-5.4</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1235,32 +1229,32 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>3. El movimiento</t>
+          <t>5. Objetos técnicos.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>3.2. Comparación de qué objetos y personas se mueven más rápido o más lento y hacia dónde.</t>
+          <t>5.4. Comprobación de la carga que soporta una estructura según su forma y sus materiales.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Ordena de más rápido a más lento a juguetes o compañeros en una carrera y señala con flechas hacia dónde se mueve cada uno.</t>
+          <t>Agrega pesos a un modelo de puente o torre hasta que se deforma o cae y compara los resultados de dos diseños.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Movimiento, reposo y tipos de trayectoria</t>
+          <t>Fuerza como empuje o tirón</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Rapidez y velocidad (2.°) necesita Posición, desplazamiento y trayectoria (5.°)</t>
+          <t>corregir_secuencia: Esfuerzo, deformación y módulo de Young (2.°) necesita Fuerza elástica y ley de Hooke (5.°)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>La comparación se mantiene cualitativa. La rapidez como magnitud y la velocidad necesitan posición y desplazamiento, y quedan en 5.°.</t>
+          <t>El tema no trabaja el módulo de Young: la etiqueta crea una secuencia invertida falsa. Se reformula como comparación de diseños, sin cuantificar el esfuerzo.</t>
         </is>
       </c>
     </row>
@@ -1275,46 +1269,154 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>G03-CIE-U1-1.1</t>
+          <t>G02-CIE-U3-3.2</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3. El movimiento</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3.2. Comparación de qué objetos y personas se mueven más rápido o más lento y hacia dónde.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Ordena de más rápido a más lento a juguetes o compañeros en una carrera y señala con flechas hacia dónde se mueve cada uno.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Movimiento, reposo y tipos de trayectoria</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>corregir_secuencia: Rapidez y velocidad (2.°) necesita Posición, desplazamiento y trayectoria (5.°)</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>La comparación se mantiene cualitativa. La rapidez como magnitud y la velocidad necesitan posición y desplazamiento, y quedan en 5.°.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>G03-CIE-U1-1.1</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F17" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>1. Medidas y fuerzas.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>1.1. Medición directa empleando diferentes instrumentos y las unidades básicas del Sistema Internacional (metro, centímetro, kilogramo, gramo y litro).</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>Mide longitudes, masas y volúmenes de objetos del entorno y expresa cada medida con su número y su unidad.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>Medición de magnitudes con instrumentos, Sistema Internacional de Unidades</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>CO 2, ENG 6, UY 3 (Sistema Internacional de Unidades; destino 3.°); prerrequisito: Medición de magnitudes con instrumentos (2.°)</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>Hoy las unidades del SI llegan en 5.°. Se introducen las básicas al medir en 3.°; la conversión y las unidades derivadas siguen en 5.°.</t>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Colombia y Uruguay lo adelantan; los países de alto desempeño no (ENG 6). Por eso solo se nombran las unidades de uso diario al medir en 3.°; conversión y unidades derivadas siguen en 5.°.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>G02-CIE-U2-2.6</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2. Energía.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2.6. Comparación de objetos colocados al sol y a la sombra para observar cómo se calientan y se enfrían.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Predice y comprueba al tacto qué objetos se calientan más al sol y cómo se enfrían al pasar a la sombra, y registra sus observaciones con dibujos.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Calentamiento y enfriamiento</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>temas_del_ciclo: G02-2.6 etiquetado con Conducción, convección y radiación (concepto de secundaria); prerrequisito: Calentamiento y enfriamiento → Temperatura y escalas termométricas (acción 1, 3.°); T4_27-P2.2 Calentamiento y enfriamiento (reforzar: 1 tema, débil)</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Se centra en calentar y enfriar y se retira la etiqueta de conducción, convección y radiación, impropia en 2.°. Queda como base de la temperatura de 3.° (acción 1).</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1482,7 @@
         <v>20</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="4">
         <f>C2-B2</f>
@@ -1426,7 +1528,7 @@
         <v>9</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="4">
         <f>C4-B4</f>

--- a/asignaturas/fisica/propuesta/Propuesta_Fisica_G02-G04.xlsx
+++ b/asignaturas/fisica/propuesta/Propuesta_Fisica_G02-G04.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Masa y peso (2.°) necesita Gravedad: atracción hacia la Tierra (hoy en ningún grado)</t>
+          <t>AU 3, ENG 3 (Gravedad: atracción hacia la Tierra, grado equivalente SV; objetivos AU-AC9S4U03 y ENG-FIS-Y5-01 del grafo); también UY 4 y SG 6; prerrequisito: Fuerzas de contacto y a distancia (G03-1.3 y 1.4, mismo tema y grado); corregir_secuencia: Masa y peso (2.°) necesita Gravedad: atracción hacia la Tierra (hoy en ningún grado)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>La gravedad no aparece en ningún grado de la malla. Se nombra de forma cualitativa en las fuerzas a distancia de 3.°; la ley de gravitación sigue en 10.°. Los imanes pasan al tema nuevo 1.7.</t>
+          <t>Australia e Inglaterra la enseñan en el equivalente a 3.°; El Salvador no la enseña como concepto. Se nombra de forma cualitativa en las fuerzas a distancia; la gravitación sigue en 10.°. Los imanes pasan al tema 1.7.</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>En 2.° se trabaja solo la masa. La distinción entre masa y peso se deja para después de la gravedad (acción 12), en 4.° o 5.°.</t>
+          <t>En 2.° se trabaja solo la masa. El peso se introduce en el tema 1.5 de 3.° (acción 19), después de la gravedad.</t>
         </is>
       </c>
     </row>
@@ -1417,6 +1417,114 @@
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Se centra en calentar y enfriar y se retira la etiqueta de conducción, convección y radiación, impropia en 2.°. Queda como base de la temperatura de 3.° (acción 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>G02-CIE-U2-2.3</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>2. Energía.</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>2.3. Identificación de fuentes naturales de energía eléctrica.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Nombra fuentes naturales que se usan para producir electricidad en El Salvador (agua de los ríos, Sol, viento y calor de los volcanes) y las relaciona con imágenes de centrales.</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Fuentes de energía renovables y no renovables</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>temas_del_ciclo: G02-2.3 etiquetado con Energía geotérmica antes de su prerrequisito Convección del manto y energía interna de la Tierra (Tierra y Espacio, confianza alta); etiquetado: «Fuentes naturales de electricidad: agua, Sol y calor de la Tierra»</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>En 2.° el calor de la Tierra solo se nombra como una fuente más de electricidad; no se explica de dónde viene ese calor. Se retira la etiqueta de energía geotérmica, que exige la energía interna de la Tierra, y el tema conserva la de fuentes de energía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>G03-CIE-U1-1.5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1. Medidas y fuerzas.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1.5. Comparación de las fuerzas de contacto y a distancia, y del peso de los objetos como la fuerza con que la Tierra los atrae.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Clasifica ejemplos de fuerzas en de contacto o a distancia, cuelga objetos de una liga y explica que el que más la estira es el que la Tierra atrae con más fuerza, es decir, el que pesa más.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Fuerzas de contacto y a distancia, Masa y peso</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>JP 2, UY 3 y 4, CO 4, SG 6 (Masa y peso, grado equivalente SV; objetivos del grafo, p. ej. SG-INT-009: el peso se debe a la fuerza gravitatoria); prerrequisito: Gravedad: atracción hacia la Tierra (G03-1.4, acción 12, tema anterior); corregir_secuencia: Masa y peso (2.°) necesita Gravedad: atracción hacia la Tierra</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>El peso se presenta como la atracción de la Tierra justo después de la gravedad, y no antes. Es cualitativo: la diferencia formal entre masa y peso (en la Luna) sigue en 5.° o después (CO 4, UY 4, SG 6).</t>
         </is>
       </c>
     </row>
